--- a/sprint_backlog/Sprint3/Sprint BacklogSprint3.xlsx
+++ b/sprint_backlog/Sprint3/Sprint BacklogSprint3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dowload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D76B510-BF1E-4A3B-A1A1-7315A5749851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A42B13-2E11-4ADF-A5A6-5084750EFBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B5253C82-4072-2C4B-808F-9C686716511B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="50">
   <si>
     <t>Sprint Backlog</t>
   </si>
@@ -178,6 +178,18 @@
   </si>
   <si>
     <t>ออกแบบฐานข้อมูล Quick Chat</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Actual Remaining</t>
+  </si>
+  <si>
+    <t>Ideal Burndown</t>
   </si>
 </sst>
 </file>
@@ -314,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -367,6 +379,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -375,19 +399,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -405,6 +420,2256 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="th-TH"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sprint 3  Remaining Estimate per Day</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$T$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Estimate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$13:$S$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$T$13:$T$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2CF7-44DE-84EC-17AF9B1F01CE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="49986208"/>
+        <c:axId val="49985248"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="49986208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Day</a:t>
+                </a:r>
+                <a:endParaRPr lang="th-TH"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="49985248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="49985248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Estimate</a:t>
+                </a:r>
+                <a:endParaRPr lang="th-TH"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="49986208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="th-TH"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sprint3</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Burndown Chart</a:t>
+            </a:r>
+            <a:endParaRPr lang="th-TH"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$T$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual Remaining</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$S$4:$S$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$T$4:$T$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B27B-4A8D-BF69-827917BB7B12}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$U$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ideal Burndown</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$S$4:$S$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$U$4:$U$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B27B-4A8D-BF69-827917BB7B12}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="87364816"/>
+        <c:axId val="87365296"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="87364816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Day</a:t>
+                </a:r>
+                <a:endParaRPr lang="th-TH"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="87365296"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="87365296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Remaining</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Estimate</a:t>
+                </a:r>
+                <a:endParaRPr lang="th-TH"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="87364816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>369094</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>976312</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>488155</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="แผนภูมิ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E229462-63A1-1112-B0CD-296359D95763}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>976313</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>146444</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>964406</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>500062</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="แผนภูมิ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B065F25-B87C-4BC8-4F65-614EA2069397}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -724,7 +2989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A130026F-C023-4C47-9AC9-41357F3A62D4}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -732,39 +2997,41 @@
     <col min="3" max="3" width="35.88671875" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
     <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="20" max="20" width="15.21875" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="50.1" customHeight="1">
+    <row r="1" spans="1:21" ht="50.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="35.25" customHeight="1"/>
-    <row r="3" spans="1:15" ht="39" customHeight="1">
-      <c r="A3" s="24" t="s">
+    <row r="2" spans="1:21" ht="35.25" customHeight="1"/>
+    <row r="3" spans="1:21" ht="39" customHeight="1">
+      <c r="A3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="19" t="s">
+      <c r="C3" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
       <c r="M3" s="17"/>
       <c r="N3" s="2" t="s">
         <v>6</v>
@@ -772,13 +3039,22 @@
       <c r="O3" s="14" t="s">
         <v>38</v>
       </c>
+      <c r="S3" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="27" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="60.95" customHeight="1">
-      <c r="A4" s="22"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="22"/>
+    <row r="4" spans="1:21" ht="60.95" customHeight="1">
+      <c r="A4" s="21"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="21"/>
       <c r="F4" s="3">
         <v>1</v>
       </c>
@@ -809,12 +3085,21 @@
         <f>SUM(E5:E41)</f>
         <v>109</v>
       </c>
+      <c r="S4" s="27">
+        <v>1</v>
+      </c>
+      <c r="T4" s="27">
+        <v>109</v>
+      </c>
+      <c r="U4" s="27">
+        <v>109</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" ht="61.5">
-      <c r="A5" s="19">
-        <v>2</v>
-      </c>
-      <c r="B5" s="19" t="s">
+    <row r="5" spans="1:21" ht="61.5">
+      <c r="A5" s="22">
+        <v>3</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -851,10 +3136,19 @@
       <c r="N5" s="2">
         <v>1</v>
       </c>
+      <c r="S5" s="27">
+        <v>2</v>
+      </c>
+      <c r="T5" s="27">
+        <v>94</v>
+      </c>
+      <c r="U5" s="27">
+        <v>91</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" ht="30" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="20"/>
+    <row r="6" spans="1:21" ht="30" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
@@ -889,10 +3183,19 @@
       <c r="N6" s="2">
         <v>2</v>
       </c>
+      <c r="S6" s="27">
+        <v>3</v>
+      </c>
+      <c r="T6" s="27">
+        <v>67</v>
+      </c>
+      <c r="U6" s="27">
+        <v>73</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" ht="30.95" customHeight="1">
-      <c r="A7" s="26"/>
-      <c r="B7" s="24" t="s">
+    <row r="7" spans="1:21" ht="30.95" customHeight="1">
+      <c r="A7" s="23"/>
+      <c r="B7" s="19" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -929,10 +3232,19 @@
       <c r="N7" s="2">
         <v>2</v>
       </c>
+      <c r="S7" s="27">
+        <v>4</v>
+      </c>
+      <c r="T7" s="27">
+        <v>67</v>
+      </c>
+      <c r="U7" s="27">
+        <v>55</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" ht="30.95" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="25"/>
+    <row r="8" spans="1:21" ht="30.95" customHeight="1">
+      <c r="A8" s="23"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="5" t="s">
         <v>32</v>
       </c>
@@ -967,10 +3279,19 @@
       <c r="N8" s="2">
         <v>2</v>
       </c>
+      <c r="S8" s="27">
+        <v>5</v>
+      </c>
+      <c r="T8" s="27">
+        <v>67</v>
+      </c>
+      <c r="U8" s="27">
+        <v>37</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" ht="33.950000000000003" customHeight="1">
-      <c r="A9" s="26"/>
-      <c r="B9" s="25"/>
+    <row r="9" spans="1:21" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="20"/>
       <c r="C9" s="8" t="s">
         <v>11</v>
       </c>
@@ -1005,10 +3326,19 @@
       <c r="N9" s="2">
         <v>2</v>
       </c>
+      <c r="S9" s="27">
+        <v>6</v>
+      </c>
+      <c r="T9" s="27">
+        <v>60</v>
+      </c>
+      <c r="U9" s="27">
+        <v>19</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" ht="61.5">
-      <c r="A10" s="26"/>
-      <c r="B10" s="25"/>
+    <row r="10" spans="1:21" ht="61.5">
+      <c r="A10" s="23"/>
+      <c r="B10" s="20"/>
       <c r="C10" s="10" t="s">
         <v>33</v>
       </c>
@@ -1043,10 +3373,19 @@
       <c r="N10" s="2">
         <v>2</v>
       </c>
+      <c r="S10" s="27">
+        <v>7</v>
+      </c>
+      <c r="T10" s="27">
+        <v>0</v>
+      </c>
+      <c r="U10" s="27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" ht="30.95" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="25"/>
+    <row r="11" spans="1:21" ht="30.95" customHeight="1">
+      <c r="A11" s="23"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="5" t="s">
         <v>13</v>
       </c>
@@ -1082,9 +3421,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="36" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="25"/>
+    <row r="12" spans="1:21" ht="36" customHeight="1">
+      <c r="A12" s="23"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="5" t="s">
         <v>14</v>
       </c>
@@ -1119,10 +3458,16 @@
       <c r="N12" s="2">
         <v>1</v>
       </c>
+      <c r="S12" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="27" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" ht="29.1" customHeight="1">
-      <c r="A13" s="26"/>
-      <c r="B13" s="22"/>
+    <row r="13" spans="1:21" ht="29.1" customHeight="1">
+      <c r="A13" s="23"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="5" t="s">
         <v>15</v>
       </c>
@@ -1157,10 +3502,16 @@
       <c r="N13" s="2">
         <v>2</v>
       </c>
+      <c r="S13" s="27">
+        <v>1</v>
+      </c>
+      <c r="T13" s="27">
+        <v>109</v>
+      </c>
     </row>
-    <row r="14" spans="1:15" ht="29.1" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="24" t="s">
+    <row r="14" spans="1:21" ht="29.1" customHeight="1">
+      <c r="A14" s="23"/>
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -1197,10 +3548,16 @@
       <c r="N14" s="2">
         <v>2</v>
       </c>
+      <c r="S14" s="27">
+        <v>2</v>
+      </c>
+      <c r="T14" s="27">
+        <v>94</v>
+      </c>
     </row>
-    <row r="15" spans="1:15" ht="51.75" customHeight="1">
-      <c r="A15" s="26"/>
-      <c r="B15" s="25"/>
+    <row r="15" spans="1:21" ht="51.75" customHeight="1">
+      <c r="A15" s="23"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="4" t="s">
         <v>31</v>
       </c>
@@ -1235,10 +3592,16 @@
       <c r="N15" s="2">
         <v>2</v>
       </c>
+      <c r="S15" s="27">
+        <v>3</v>
+      </c>
+      <c r="T15" s="27">
+        <v>67</v>
+      </c>
     </row>
-    <row r="16" spans="1:15" ht="40.5" customHeight="1">
-      <c r="A16" s="26"/>
-      <c r="B16" s="25"/>
+    <row r="16" spans="1:21" ht="40.5" customHeight="1">
+      <c r="A16" s="23"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="8" t="s">
         <v>11</v>
       </c>
@@ -1273,10 +3636,16 @@
       <c r="N16" s="2">
         <v>2</v>
       </c>
+      <c r="S16" s="27">
+        <v>4</v>
+      </c>
+      <c r="T16" s="27">
+        <v>67</v>
+      </c>
     </row>
-    <row r="17" spans="1:14" ht="50.25" customHeight="1">
-      <c r="A17" s="26"/>
-      <c r="B17" s="25"/>
+    <row r="17" spans="1:20" ht="50.25" customHeight="1">
+      <c r="A17" s="23"/>
+      <c r="B17" s="20"/>
       <c r="C17" s="4" t="s">
         <v>34</v>
       </c>
@@ -1311,10 +3680,16 @@
       <c r="N17" s="2">
         <v>2</v>
       </c>
+      <c r="S17" s="27">
+        <v>5</v>
+      </c>
+      <c r="T17" s="27">
+        <v>67</v>
+      </c>
     </row>
-    <row r="18" spans="1:14" ht="40.5" customHeight="1">
-      <c r="A18" s="26"/>
-      <c r="B18" s="25"/>
+    <row r="18" spans="1:20" ht="40.5" customHeight="1">
+      <c r="A18" s="23"/>
+      <c r="B18" s="20"/>
       <c r="C18" s="5" t="s">
         <v>13</v>
       </c>
@@ -1349,10 +3724,16 @@
       <c r="N18" s="2">
         <v>2</v>
       </c>
+      <c r="S18" s="27">
+        <v>6</v>
+      </c>
+      <c r="T18" s="27">
+        <v>60</v>
+      </c>
     </row>
-    <row r="19" spans="1:14" ht="40.5" customHeight="1">
-      <c r="A19" s="26"/>
-      <c r="B19" s="25"/>
+    <row r="19" spans="1:20" ht="40.5" customHeight="1">
+      <c r="A19" s="23"/>
+      <c r="B19" s="20"/>
       <c r="C19" s="5" t="s">
         <v>14</v>
       </c>
@@ -1387,10 +3768,16 @@
       <c r="N19" s="2">
         <v>2</v>
       </c>
+      <c r="S19" s="27">
+        <v>7</v>
+      </c>
+      <c r="T19" s="27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:14" ht="40.5" customHeight="1">
-      <c r="A20" s="26"/>
-      <c r="B20" s="22"/>
+    <row r="20" spans="1:20" ht="40.5" customHeight="1">
+      <c r="A20" s="23"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="5" t="s">
         <v>15</v>
       </c>
@@ -1426,9 +3813,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="36" customHeight="1">
-      <c r="A21" s="26"/>
-      <c r="B21" s="24" t="s">
+    <row r="21" spans="1:20" ht="36" customHeight="1">
+      <c r="A21" s="23"/>
+      <c r="B21" s="19" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="6" t="s">
@@ -1466,9 +3853,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="36" customHeight="1">
-      <c r="A22" s="26"/>
-      <c r="B22" s="25"/>
+    <row r="22" spans="1:20" ht="36" customHeight="1">
+      <c r="A22" s="23"/>
+      <c r="B22" s="20"/>
       <c r="C22" s="5" t="s">
         <v>45</v>
       </c>
@@ -1504,9 +3891,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="36" customHeight="1">
-      <c r="A23" s="26"/>
-      <c r="B23" s="25"/>
+    <row r="23" spans="1:20" ht="36" customHeight="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="8" t="s">
         <v>11</v>
       </c>
@@ -1542,9 +3929,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="69" customHeight="1">
-      <c r="A24" s="26"/>
-      <c r="B24" s="25"/>
+    <row r="24" spans="1:20" ht="69" customHeight="1">
+      <c r="A24" s="23"/>
+      <c r="B24" s="20"/>
       <c r="C24" s="10" t="s">
         <v>44</v>
       </c>
@@ -1580,9 +3967,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="36" customHeight="1">
-      <c r="A25" s="26"/>
-      <c r="B25" s="25"/>
+    <row r="25" spans="1:20" ht="36" customHeight="1">
+      <c r="A25" s="23"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="5" t="s">
         <v>13</v>
       </c>
@@ -1618,9 +4005,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="36" customHeight="1">
-      <c r="A26" s="26"/>
-      <c r="B26" s="25"/>
+    <row r="26" spans="1:20" ht="36" customHeight="1">
+      <c r="A26" s="23"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="5" t="s">
         <v>14</v>
       </c>
@@ -1656,9 +4043,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A27" s="26"/>
-      <c r="B27" s="22"/>
+    <row r="27" spans="1:20" ht="33.75" customHeight="1">
+      <c r="A27" s="23"/>
+      <c r="B27" s="21"/>
       <c r="C27" s="5" t="s">
         <v>15</v>
       </c>
@@ -1694,9 +4081,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A28" s="26"/>
-      <c r="B28" s="24" t="s">
+    <row r="28" spans="1:20" ht="33.75" customHeight="1">
+      <c r="A28" s="23"/>
+      <c r="B28" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -1734,9 +4121,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A29" s="26"/>
-      <c r="B29" s="25"/>
+    <row r="29" spans="1:20" ht="33.75" customHeight="1">
+      <c r="A29" s="23"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="5" t="s">
         <v>30</v>
       </c>
@@ -1772,9 +4159,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A30" s="26"/>
-      <c r="B30" s="25"/>
+    <row r="30" spans="1:20" ht="33.75" customHeight="1">
+      <c r="A30" s="23"/>
+      <c r="B30" s="20"/>
       <c r="C30" s="8" t="s">
         <v>11</v>
       </c>
@@ -1810,9 +4197,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="57" customHeight="1">
-      <c r="A31" s="26"/>
-      <c r="B31" s="25"/>
+    <row r="31" spans="1:20" ht="57" customHeight="1">
+      <c r="A31" s="23"/>
+      <c r="B31" s="20"/>
       <c r="C31" s="10" t="s">
         <v>12</v>
       </c>
@@ -1848,9 +4235,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A32" s="26"/>
-      <c r="B32" s="25"/>
+    <row r="32" spans="1:20" ht="33.75" customHeight="1">
+      <c r="A32" s="23"/>
+      <c r="B32" s="20"/>
       <c r="C32" s="5" t="s">
         <v>13</v>
       </c>
@@ -1887,8 +4274,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A33" s="26"/>
-      <c r="B33" s="25"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="20"/>
       <c r="C33" s="5" t="s">
         <v>14</v>
       </c>
@@ -1925,8 +4312,8 @@
       </c>
     </row>
     <row r="34" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A34" s="26"/>
-      <c r="B34" s="22"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="21"/>
       <c r="C34" s="5" t="s">
         <v>15</v>
       </c>
@@ -1963,8 +4350,8 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A35" s="26"/>
-      <c r="B35" s="19" t="s">
+      <c r="A35" s="23"/>
+      <c r="B35" s="22" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -2003,8 +4390,8 @@
       </c>
     </row>
     <row r="36" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
       <c r="C36" s="5" t="s">
         <v>18</v>
       </c>
@@ -2041,8 +4428,8 @@
       </c>
     </row>
     <row r="37" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
       <c r="C37" s="5" t="s">
         <v>19</v>
       </c>
@@ -2079,8 +4466,8 @@
       </c>
     </row>
     <row r="38" spans="1:14" ht="36.75" customHeight="1">
-      <c r="A38" s="26"/>
-      <c r="B38" s="26"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
       <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
@@ -2117,8 +4504,8 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
       <c r="C39" s="5" t="s">
         <v>21</v>
       </c>
@@ -2155,8 +4542,8 @@
       </c>
     </row>
     <row r="40" spans="1:14" ht="30" customHeight="1">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
       <c r="C40" s="5" t="s">
         <v>22</v>
       </c>
@@ -2193,8 +4580,8 @@
       </c>
     </row>
     <row r="41" spans="1:14" ht="30" customHeight="1">
-      <c r="A41" s="20"/>
-      <c r="B41" s="20"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
       <c r="C41" s="5" t="s">
         <v>23</v>
       </c>
@@ -2232,6 +4619,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="B21:B27"/>
     <mergeCell ref="B28:B34"/>
     <mergeCell ref="B35:B41"/>
@@ -2239,14 +4632,9 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="B14:B20"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>